--- a/test-attachments/mm-datacenter-audit.xlsx
+++ b/test-attachments/mm-datacenter-audit.xlsx
@@ -3,8 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Servers" sheetId="1" r:id="rId1"/>
-    <sheet name="Network Equipment" sheetId="2" r:id="rId2"/>
+    <sheet name="Production Servers" sheetId="1" r:id="rId1"/>
+    <sheet name="Network Infrastructure" sheetId="2" r:id="rId2"/>
+    <sheet name="Excluded Labs" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,1270 +399,1530 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:F66"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Asset Tag</v>
+        <v>Server Tag</v>
       </c>
       <c r="B1" t="str">
-        <v>Host Type</v>
+        <v>Host Model</v>
       </c>
       <c r="C1" t="str">
-        <v>CPU Cores</v>
+        <v>Cores</v>
       </c>
       <c r="D1" t="str">
-        <v>RAM GB</v>
+        <v>Memory</v>
       </c>
       <c r="E1" t="str">
+        <v>IP Address</v>
+      </c>
+      <c r="F1" t="str">
         <v>Environment</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TAG-SRV-1</v>
+        <v>DC-PROD-SRV-1</v>
       </c>
       <c r="B2" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C2" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D2" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E2" t="str">
-        <v>Prod</v>
+        <v>10.5.10.1</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TAG-SRV-2</v>
+        <v>DC-PROD-SRV-2</v>
       </c>
       <c r="B3" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C3" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D3" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E3" t="str">
-        <v>Prod</v>
+        <v>10.5.10.2</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TAG-SRV-3</v>
+        <v>DC-PROD-SRV-3</v>
       </c>
       <c r="B4" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C4" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D4" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E4" t="str">
-        <v>Prod</v>
+        <v>10.5.10.3</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TAG-SRV-4</v>
+        <v>DC-PROD-SRV-4</v>
       </c>
       <c r="B5" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C5" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D5" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E5" t="str">
-        <v>Prod</v>
+        <v>10.5.10.4</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TAG-SRV-5</v>
+        <v>DC-PROD-SRV-5</v>
       </c>
       <c r="B6" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C6" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D6" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E6" t="str">
-        <v>Prod</v>
+        <v>10.5.10.5</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TAG-SRV-6</v>
+        <v>DC-PROD-SRV-6</v>
       </c>
       <c r="B7" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C7" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D7" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E7" t="str">
-        <v>Prod</v>
+        <v>10.5.10.6</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>TAG-SRV-7</v>
+        <v>DC-PROD-SRV-7</v>
       </c>
       <c r="B8" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C8" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D8" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E8" t="str">
-        <v>Prod</v>
+        <v>10.5.10.7</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TAG-SRV-8</v>
+        <v>DC-PROD-SRV-8</v>
       </c>
       <c r="B9" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C9" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D9" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E9" t="str">
-        <v>Prod</v>
+        <v>10.5.10.8</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>TAG-SRV-9</v>
+        <v>DC-PROD-SRV-9</v>
       </c>
       <c r="B10" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C10" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D10" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E10" t="str">
-        <v>Prod</v>
+        <v>10.5.10.9</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>TAG-SRV-10</v>
+        <v>DC-PROD-SRV-10</v>
       </c>
       <c r="B11" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C11" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D11" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E11" t="str">
-        <v>Prod</v>
+        <v>10.5.10.10</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>TAG-SRV-11</v>
+        <v>DC-PROD-SRV-11</v>
       </c>
       <c r="B12" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C12" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D12" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E12" t="str">
-        <v>Prod</v>
+        <v>10.5.10.11</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TAG-SRV-12</v>
+        <v>DC-PROD-SRV-12</v>
       </c>
       <c r="B13" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C13" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D13" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E13" t="str">
-        <v>Prod</v>
+        <v>10.5.10.12</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>TAG-SRV-13</v>
+        <v>DC-PROD-SRV-13</v>
       </c>
       <c r="B14" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C14" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D14" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E14" t="str">
-        <v>Prod</v>
+        <v>10.5.10.13</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>TAG-SRV-14</v>
+        <v>DC-PROD-SRV-14</v>
       </c>
       <c r="B15" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C15" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D15" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E15" t="str">
-        <v>Prod</v>
+        <v>10.5.10.14</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>TAG-SRV-15</v>
+        <v>DC-PROD-SRV-15</v>
       </c>
       <c r="B16" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C16" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D16" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E16" t="str">
-        <v>Prod</v>
+        <v>10.5.10.15</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>TAG-SRV-16</v>
+        <v>DC-PROD-SRV-16</v>
       </c>
       <c r="B17" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C17" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D17" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E17" t="str">
-        <v>Prod</v>
+        <v>10.5.10.16</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TAG-SRV-17</v>
+        <v>DC-PROD-SRV-17</v>
       </c>
       <c r="B18" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C18" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D18" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E18" t="str">
-        <v>Prod</v>
+        <v>10.5.10.17</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>TAG-SRV-18</v>
+        <v>DC-PROD-SRV-18</v>
       </c>
       <c r="B19" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C19" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D19" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E19" t="str">
-        <v>Prod</v>
+        <v>10.5.10.18</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>TAG-SRV-19</v>
+        <v>DC-PROD-SRV-19</v>
       </c>
       <c r="B20" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C20" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D20" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E20" t="str">
-        <v>Prod</v>
+        <v>10.5.10.19</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>TAG-SRV-20</v>
+        <v>DC-PROD-SRV-20</v>
       </c>
       <c r="B21" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C21" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D21" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E21" t="str">
-        <v>Prod</v>
+        <v>10.5.10.20</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>TAG-SRV-21</v>
+        <v>DC-PROD-SRV-21</v>
       </c>
       <c r="B22" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C22" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D22" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E22" t="str">
-        <v>Prod</v>
+        <v>10.5.10.21</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>TAG-SRV-22</v>
+        <v>DC-PROD-SRV-22</v>
       </c>
       <c r="B23" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C23" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D23" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E23" t="str">
-        <v>Prod</v>
+        <v>10.5.10.22</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>TAG-SRV-23</v>
+        <v>DC-PROD-SRV-23</v>
       </c>
       <c r="B24" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C24" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D24" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E24" t="str">
-        <v>Prod</v>
+        <v>10.5.10.23</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>TAG-SRV-24</v>
+        <v>DC-PROD-SRV-24</v>
       </c>
       <c r="B25" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C25" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D25" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E25" t="str">
-        <v>Prod</v>
+        <v>10.5.10.24</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>TAG-SRV-25</v>
+        <v>DC-PROD-SRV-25</v>
       </c>
       <c r="B26" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C26" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D26" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E26" t="str">
-        <v>Prod</v>
+        <v>10.5.10.25</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>TAG-SRV-26</v>
+        <v>DC-PROD-SRV-26</v>
       </c>
       <c r="B27" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C27" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D27" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E27" t="str">
-        <v>Prod</v>
+        <v>10.5.10.26</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>TAG-SRV-27</v>
+        <v>DC-PROD-SRV-27</v>
       </c>
       <c r="B28" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C28" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D28" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E28" t="str">
-        <v>Prod</v>
+        <v>10.5.10.27</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>TAG-SRV-28</v>
+        <v>DC-PROD-SRV-28</v>
       </c>
       <c r="B29" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C29" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D29" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E29" t="str">
-        <v>Prod</v>
+        <v>10.5.10.28</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>TAG-SRV-29</v>
+        <v>DC-PROD-SRV-29</v>
       </c>
       <c r="B30" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C30" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D30" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E30" t="str">
-        <v>Prod</v>
+        <v>10.5.10.29</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>TAG-SRV-30</v>
+        <v>DC-PROD-SRV-30</v>
       </c>
       <c r="B31" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C31" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D31" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E31" t="str">
-        <v>Prod</v>
+        <v>10.5.10.30</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>TAG-SRV-31</v>
+        <v>DC-PROD-SRV-31</v>
       </c>
       <c r="B32" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C32" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D32" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E32" t="str">
-        <v>Prod</v>
+        <v>10.5.10.31</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>TAG-SRV-32</v>
+        <v>DC-PROD-SRV-32</v>
       </c>
       <c r="B33" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C33" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D33" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E33" t="str">
-        <v>Prod</v>
+        <v>10.5.10.32</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>TAG-SRV-33</v>
+        <v>DC-PROD-SRV-33</v>
       </c>
       <c r="B34" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C34" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D34" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E34" t="str">
-        <v>Prod</v>
+        <v>10.5.10.33</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>TAG-SRV-34</v>
+        <v>DC-PROD-SRV-34</v>
       </c>
       <c r="B35" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C35" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D35" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E35" t="str">
-        <v>Prod</v>
+        <v>10.5.10.34</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>TAG-SRV-35</v>
+        <v>DC-PROD-SRV-35</v>
       </c>
       <c r="B36" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C36" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D36" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E36" t="str">
-        <v>Prod</v>
+        <v>10.5.10.35</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>TAG-SRV-36</v>
+        <v>DC-PROD-SRV-36</v>
       </c>
       <c r="B37" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C37" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D37" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E37" t="str">
-        <v>Prod</v>
+        <v>10.5.10.36</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>TAG-SRV-37</v>
+        <v>DC-PROD-SRV-37</v>
       </c>
       <c r="B38" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C38" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D38" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E38" t="str">
-        <v>Prod</v>
+        <v>10.5.10.37</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>TAG-SRV-38</v>
+        <v>DC-PROD-SRV-38</v>
       </c>
       <c r="B39" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C39" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D39" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E39" t="str">
-        <v>Prod</v>
+        <v>10.5.10.38</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>TAG-SRV-39</v>
+        <v>DC-PROD-SRV-39</v>
       </c>
       <c r="B40" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C40" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D40" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E40" t="str">
-        <v>Prod</v>
+        <v>10.5.10.39</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>TAG-SRV-40</v>
+        <v>DC-PROD-SRV-40</v>
       </c>
       <c r="B41" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C41" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D41" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E41" t="str">
-        <v>Prod</v>
+        <v>10.5.10.40</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>TAG-SRV-41</v>
+        <v>DC-PROD-SRV-41</v>
       </c>
       <c r="B42" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C42" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D42" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E42" t="str">
-        <v>Prod</v>
+        <v>10.5.10.41</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>TAG-SRV-42</v>
+        <v>DC-PROD-SRV-42</v>
       </c>
       <c r="B43" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C43" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D43" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E43" t="str">
-        <v>Prod</v>
+        <v>10.5.10.42</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>TAG-SRV-43</v>
+        <v>DC-PROD-SRV-43</v>
       </c>
       <c r="B44" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C44" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D44" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E44" t="str">
-        <v>Prod</v>
+        <v>10.5.10.43</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>TAG-SRV-44</v>
+        <v>DC-PROD-SRV-44</v>
       </c>
       <c r="B45" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C45" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D45" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E45" t="str">
-        <v>Prod</v>
+        <v>10.5.10.44</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>TAG-SRV-45</v>
+        <v>DC-PROD-SRV-45</v>
       </c>
       <c r="B46" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C46" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D46" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E46" t="str">
-        <v>Prod</v>
+        <v>10.5.10.45</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>TAG-SRV-46</v>
+        <v>DC-PROD-SRV-46</v>
       </c>
       <c r="B47" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C47" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D47" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E47" t="str">
-        <v>Prod</v>
+        <v>10.5.10.46</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>TAG-SRV-47</v>
+        <v>DC-PROD-SRV-47</v>
       </c>
       <c r="B48" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C48" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D48" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E48" t="str">
-        <v>Prod</v>
+        <v>10.5.10.47</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>TAG-SRV-48</v>
+        <v>DC-PROD-SRV-48</v>
       </c>
       <c r="B49" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C49" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D49" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E49" t="str">
-        <v>Prod</v>
+        <v>10.5.10.48</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>TAG-SRV-49</v>
+        <v>DC-PROD-SRV-49</v>
       </c>
       <c r="B50" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C50" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D50" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E50" t="str">
-        <v>Prod</v>
+        <v>10.5.10.49</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>TAG-SRV-50</v>
+        <v>DC-PROD-SRV-50</v>
       </c>
       <c r="B51" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C51" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D51" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E51" t="str">
-        <v>Prod</v>
+        <v>10.5.10.50</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>TAG-SRV-51</v>
+        <v>DC-PROD-SRV-51</v>
       </c>
       <c r="B52" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C52" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D52" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E52" t="str">
-        <v>Prod</v>
+        <v>10.5.10.51</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>TAG-SRV-52</v>
+        <v>DC-PROD-SRV-52</v>
       </c>
       <c r="B53" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C53" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D53" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E53" t="str">
-        <v>Prod</v>
+        <v>10.5.10.52</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>TAG-SRV-53</v>
+        <v>DC-PROD-SRV-53</v>
       </c>
       <c r="B54" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C54" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D54" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E54" t="str">
-        <v>Prod</v>
+        <v>10.5.10.53</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>TAG-SRV-54</v>
+        <v>DC-PROD-SRV-54</v>
       </c>
       <c r="B55" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C55" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D55" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E55" t="str">
-        <v>Prod</v>
+        <v>10.5.10.54</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>TAG-SRV-55</v>
+        <v>DC-PROD-SRV-55</v>
       </c>
       <c r="B56" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C56" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D56" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E56" t="str">
-        <v>Prod</v>
+        <v>10.5.10.55</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>TAG-SRV-56</v>
+        <v>DC-PROD-SRV-56</v>
       </c>
       <c r="B57" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C57" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D57" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E57" t="str">
-        <v>Prod</v>
+        <v>10.5.10.56</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>TAG-SRV-57</v>
+        <v>DC-PROD-SRV-57</v>
       </c>
       <c r="B58" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C58" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D58" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E58" t="str">
-        <v>Prod</v>
+        <v>10.5.10.57</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>TAG-SRV-58</v>
+        <v>DC-PROD-SRV-58</v>
       </c>
       <c r="B59" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C59" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D59" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E59" t="str">
-        <v>Prod</v>
+        <v>10.5.10.58</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>TAG-SRV-59</v>
+        <v>DC-PROD-SRV-59</v>
       </c>
       <c r="B60" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C60" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D60" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E60" t="str">
-        <v>Prod</v>
+        <v>10.5.10.59</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>TAG-SRV-60</v>
+        <v>DC-PROD-SRV-60</v>
       </c>
       <c r="B61" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C61" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D61" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E61" t="str">
-        <v>Prod</v>
+        <v>10.5.10.60</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>TAG-SRV-61</v>
+        <v>DC-PROD-SRV-61</v>
       </c>
       <c r="B62" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C62" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D62" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E62" t="str">
-        <v>Prod</v>
+        <v>10.5.10.61</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>TAG-SRV-62</v>
+        <v>DC-PROD-SRV-62</v>
       </c>
       <c r="B63" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C63" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D63" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E63" t="str">
-        <v>Prod</v>
+        <v>10.5.10.62</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>TAG-SRV-63</v>
+        <v>DC-PROD-SRV-63</v>
       </c>
       <c r="B64" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C64" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D64" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E64" t="str">
-        <v>Prod</v>
+        <v>10.5.10.63</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>TAG-SRV-64</v>
+        <v>DC-PROD-SRV-64</v>
       </c>
       <c r="B65" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C65" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D65" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E65" t="str">
-        <v>Prod</v>
+        <v>10.5.10.64</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Production</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>TAG-SRV-65</v>
+        <v>DC-PROD-SRV-65</v>
       </c>
       <c r="B66" t="str">
-        <v>Production Linux Host</v>
+        <v>Dell PowerEdge R750</v>
       </c>
       <c r="C66" t="str">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D66" t="str">
-        <v>64</v>
+        <v>128 GB</v>
       </c>
       <c r="E66" t="str">
-        <v>Prod</v>
+        <v>10.5.10.65</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Production</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F66"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Switch ID</v>
+        <v>Device Tag</v>
       </c>
       <c r="B1" t="str">
-        <v>Model</v>
+        <v>Hardware Type</v>
       </c>
       <c r="C1" t="str">
+        <v>Vendor</v>
+      </c>
+      <c r="D1" t="str">
         <v>Ports</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Location</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SW-CORE-1</v>
+        <v>NET-SW-1</v>
       </c>
       <c r="B2" t="str">
-        <v>Cisco Catalyst 9300</v>
+        <v>Network Switch</v>
       </c>
       <c r="C2" t="str">
-        <v>48</v>
+        <v>Cisco Nexus 9000</v>
       </c>
       <c r="D2" t="str">
-        <v>DC-Row-1</v>
+        <v>48x10G</v>
+      </c>
+      <c r="E2" t="str">
+        <v>DC Row A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SW-CORE-2</v>
+        <v>NET-SW-2</v>
       </c>
       <c r="B3" t="str">
-        <v>Cisco Catalyst 9300</v>
+        <v>Network Switch</v>
       </c>
       <c r="C3" t="str">
-        <v>48</v>
+        <v>Cisco Nexus 9000</v>
       </c>
       <c r="D3" t="str">
-        <v>DC-Row-1</v>
+        <v>48x10G</v>
+      </c>
+      <c r="E3" t="str">
+        <v>DC Row A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SW-CORE-3</v>
+        <v>NET-SW-3</v>
       </c>
       <c r="B4" t="str">
-        <v>Cisco Catalyst 9300</v>
+        <v>Network Switch</v>
       </c>
       <c r="C4" t="str">
-        <v>48</v>
+        <v>Cisco Nexus 9000</v>
       </c>
       <c r="D4" t="str">
-        <v>DC-Row-1</v>
+        <v>48x10G</v>
+      </c>
+      <c r="E4" t="str">
+        <v>DC Row A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SW-CORE-4</v>
+        <v>NET-SW-4</v>
       </c>
       <c r="B5" t="str">
-        <v>Cisco Catalyst 9300</v>
+        <v>Network Switch</v>
       </c>
       <c r="C5" t="str">
-        <v>48</v>
+        <v>Cisco Nexus 9000</v>
       </c>
       <c r="D5" t="str">
-        <v>DC-Row-1</v>
+        <v>48x10G</v>
+      </c>
+      <c r="E5" t="str">
+        <v>DC Row A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SW-CORE-5</v>
+        <v>NET-SW-5</v>
       </c>
       <c r="B6" t="str">
-        <v>Cisco Catalyst 9300</v>
+        <v>Network Switch</v>
       </c>
       <c r="C6" t="str">
-        <v>48</v>
+        <v>Cisco Nexus 9000</v>
       </c>
       <c r="D6" t="str">
-        <v>DC-Row-1</v>
+        <v>48x10G</v>
+      </c>
+      <c r="E6" t="str">
+        <v>DC Row A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SW-CORE-6</v>
+        <v>NET-SW-6</v>
       </c>
       <c r="B7" t="str">
-        <v>Cisco Catalyst 9300</v>
+        <v>Network Switch</v>
       </c>
       <c r="C7" t="str">
-        <v>48</v>
+        <v>Cisco Nexus 9000</v>
       </c>
       <c r="D7" t="str">
-        <v>DC-Row-1</v>
+        <v>48x10G</v>
+      </c>
+      <c r="E7" t="str">
+        <v>DC Row A</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SW-CORE-7</v>
+        <v>NET-SW-7</v>
       </c>
       <c r="B8" t="str">
-        <v>Cisco Catalyst 9300</v>
+        <v>Network Switch</v>
       </c>
       <c r="C8" t="str">
-        <v>48</v>
+        <v>Cisco Nexus 9000</v>
       </c>
       <c r="D8" t="str">
-        <v>DC-Row-1</v>
+        <v>48x10G</v>
+      </c>
+      <c r="E8" t="str">
+        <v>DC Row A</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SW-CORE-8</v>
+        <v>NET-SW-8</v>
       </c>
       <c r="B9" t="str">
-        <v>Cisco Catalyst 9300</v>
+        <v>Network Switch</v>
       </c>
       <c r="C9" t="str">
-        <v>48</v>
+        <v>Cisco Nexus 9000</v>
       </c>
       <c r="D9" t="str">
-        <v>DC-Row-1</v>
+        <v>48x10G</v>
+      </c>
+      <c r="E9" t="str">
+        <v>DC Row A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Decommissioned Node</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>OLD-SRV-99</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Retired</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TEST-BOX-01</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Dev/Test Only - Do not monitor</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
   </ignoredErrors>
 </worksheet>
 </file>